--- a/.schema/MHR_SHOKUI_NINKA.xlsx
+++ b/.schema/MHR_SHOKUI_NINKA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{411231E5-6608-4421-BA5C-67069D45EEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82C8A73-C33F-4CD9-9B39-A95833FA97F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0B9089A8-A578-47DE-B450-3B58C9511DE5}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E482EAC-8FBE-4D26-9D55-F765726269D5}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MHR_SHOKUI_NINKA" sheetId="2" r:id="rId1"/>
@@ -38,10 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t>99</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
   <si>
     <t>.+</t>
   </si>
@@ -64,10 +61,10 @@
     <t>TEKIYO_BI</t>
   </si>
   <si>
-    <t>KENGEN_KB</t>
+    <t>KENGEN_B</t>
   </si>
   <si>
-    <t>KINO_NM</t>
+    <t>TABLE_RE</t>
   </si>
   <si>
     <t>SHOKUI_ID</t>
@@ -81,7 +78,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ h:mm:ss.000"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -114,7 +111,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -168,7 +164,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -187,13 +183,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="180"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{87AE5D5A-EEA4-48DA-A9C3-2A29BF93A813}"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{A02C0AD0-FDB7-476E-9B51-CF46F0E99680}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -504,56 +503,78 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34BAD067-C0FD-498E-B9C8-B1819F730CA4}">
-  <dimension ref="A2:J3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB75501-AA93-4917-96DA-843BFCA602F1}">
+  <dimension ref="A2:T11"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.09765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.69921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.796875" style="1"/>
+    <col min="1" max="6" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.69921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.796875" style="1"/>
+    <col min="12" max="19" width="3.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:20" s="7" customFormat="1" ht="86.4" x14ac:dyDescent="0.45">
       <c r="A2" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="7">
+        <v>128</v>
+      </c>
+      <c r="M2" s="7">
+        <v>64</v>
+      </c>
+      <c r="N2" s="7">
+        <v>32</v>
+      </c>
+      <c r="O2" s="7">
+        <v>16</v>
+      </c>
+      <c r="P2" s="7">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="6" t="s">
+      <c r="Q2" s="7">
         <v>4</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="6" t="s">
+      <c r="R2" s="7">
         <v>2</v>
       </c>
+      <c r="S2" s="7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>0</v>
       </c>
@@ -561,24 +582,513 @@
         <v>0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2">
+        <f>T3</f>
         <v>0</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="3"/>
+      <c r="G3" s="3">
+        <v>46086</v>
+      </c>
       <c r="H3" s="2">
         <v>0</v>
       </c>
-      <c r="I3" s="3"/>
+      <c r="I3" s="3">
+        <v>46086</v>
+      </c>
       <c r="J3" s="2">
         <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1">
+        <v>0</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0</v>
+      </c>
+      <c r="T3" s="1">
+        <f>SUMPRODUCT(L$2:S$2,L3:S3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" ref="D4:D10" si="0">T4</f>
+        <v>1</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3">
+        <v>46086</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1">
+        <v>1</v>
+      </c>
+      <c r="T4" s="1">
+        <f t="shared" ref="T4:T10" si="1">SUMPRODUCT(L$2:S$2,L4:S4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>46086</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1">
+        <v>1</v>
+      </c>
+      <c r="T5" s="1">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A6" s="2">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>46086</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+      <c r="R6" s="1">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1">
+        <v>1</v>
+      </c>
+      <c r="T6" s="1">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A7" s="2">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>46086</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>1</v>
+      </c>
+      <c r="R7" s="1">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1">
+        <v>1</v>
+      </c>
+      <c r="T7" s="1">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>46086</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>1</v>
+      </c>
+      <c r="R8" s="1">
+        <v>1</v>
+      </c>
+      <c r="S8" s="1">
+        <v>1</v>
+      </c>
+      <c r="T8" s="1">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A9" s="2">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3">
+        <v>46086</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>1</v>
+      </c>
+      <c r="R9" s="1">
+        <v>1</v>
+      </c>
+      <c r="S9" s="1">
+        <v>1</v>
+      </c>
+      <c r="T9" s="1">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="0"/>
+        <v>127</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>46086</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>1</v>
+      </c>
+      <c r="R10" s="1">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1">
+        <v>1</v>
+      </c>
+      <c r="T10" s="1">
+        <f t="shared" si="1"/>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A11" s="2">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" ref="D11" si="2">T11</f>
+        <v>255</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="3">
+        <v>46086</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3">
+        <v>46086</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1">
+        <v>1</v>
+      </c>
+      <c r="O11" s="1">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>1</v>
+      </c>
+      <c r="R11" s="1">
+        <v>1</v>
+      </c>
+      <c r="S11" s="1">
+        <v>1</v>
+      </c>
+      <c r="T11" s="1">
+        <f t="shared" ref="T11" si="3">SUMPRODUCT(L$2:S$2,L11:S11)</f>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:J3" xr:uid="{36069F44-DF99-470C-8741-B020A5CB5ECE}"/>
+  <autoFilter ref="A2:J3" xr:uid="{6098AB44-EDF3-465E-A682-27100DC7E3D7}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/.schema/MHR_SHOKUI_NINKA.xlsx
+++ b/.schema/MHR_SHOKUI_NINKA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82C8A73-C33F-4CD9-9B39-A95833FA97F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D92C80A-F160-4E5F-B7D6-ADE746C89712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9E482EAC-8FBE-4D26-9D55-F765726269D5}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="12">
   <si>
     <t>.+</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>BUSHO_ID</t>
+  </si>
+  <si>
+    <t>« NULL »</t>
   </si>
 </sst>
 </file>
@@ -186,7 +189,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" textRotation="180"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" textRotation="180"/>
     </xf>
   </cellXfs>
@@ -507,7 +510,8 @@
   <dimension ref="A2:T11"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="6" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="5.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.69921875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.5" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.69921875" style="1" bestFit="1" customWidth="1"/>
@@ -588,16 +592,22 @@
         <f>T3</f>
         <v>0</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="G3" s="3">
-        <v>46086</v>
+        <f ca="1">NOW()</f>
+        <v>46087.424930092595</v>
       </c>
       <c r="H3" s="2">
         <v>0</v>
       </c>
       <c r="I3" s="3">
-        <v>46086</v>
+        <f t="shared" ref="I3:I11" ca="1" si="0">NOW()</f>
+        <v>46087.424930092595</v>
       </c>
       <c r="J3" s="2">
         <v>0</v>
@@ -633,28 +643,34 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <f t="shared" ref="D4:D10" si="0">T4</f>
-        <v>1</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+        <f t="shared" ref="D4:D10" si="1">T4</f>
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="G4" s="3">
-        <v>46086</v>
+        <f t="shared" ref="G4:G11" ca="1" si="2">NOW()</f>
+        <v>46087.424930092595</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
       </c>
       <c r="I4" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="J4" s="2">
         <v>0</v>
@@ -684,34 +700,40 @@
         <v>1</v>
       </c>
       <c r="T4" s="1">
-        <f t="shared" ref="T4:T10" si="1">SUMPRODUCT(L$2:S$2,L4:S4)</f>
+        <f t="shared" ref="T4:T10" si="3">SUMPRODUCT(L$2:S$2,L4:S4)</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2">
         <v>2</v>
       </c>
-      <c r="B5" s="2">
-        <v>0</v>
-      </c>
       <c r="C5" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="G5" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="J5" s="2">
         <v>0</v>
@@ -741,34 +763,40 @@
         <v>1</v>
       </c>
       <c r="T5" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2">
         <v>3</v>
       </c>
-      <c r="B6" s="2">
-        <v>0</v>
-      </c>
       <c r="C6" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="G6" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="H6" s="2">
         <v>0</v>
       </c>
       <c r="I6" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="J6" s="2">
         <v>0</v>
@@ -798,34 +826,40 @@
         <v>1</v>
       </c>
       <c r="T6" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2">
         <v>4</v>
       </c>
-      <c r="B7" s="2">
-        <v>0</v>
-      </c>
       <c r="C7" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="G7" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="H7" s="2">
         <v>0</v>
       </c>
       <c r="I7" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="J7" s="2">
         <v>0</v>
@@ -855,34 +889,40 @@
         <v>1</v>
       </c>
       <c r="T7" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2">
         <v>5</v>
       </c>
-      <c r="B8" s="2">
-        <v>0</v>
-      </c>
       <c r="C8" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="G8" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="H8" s="2">
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
@@ -912,34 +952,40 @@
         <v>1</v>
       </c>
       <c r="T8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2">
         <v>6</v>
       </c>
-      <c r="B9" s="2">
-        <v>0</v>
-      </c>
       <c r="C9" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="G9" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="H9" s="2">
         <v>0</v>
       </c>
       <c r="I9" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="J9" s="2">
         <v>0</v>
@@ -969,34 +1015,40 @@
         <v>1</v>
       </c>
       <c r="T9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10" s="2">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2">
         <v>7</v>
       </c>
-      <c r="B10" s="2">
-        <v>0</v>
-      </c>
       <c r="C10" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>127</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="G10" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="H10" s="2">
         <v>0</v>
       </c>
       <c r="I10" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="J10" s="2">
         <v>0</v>
@@ -1026,34 +1078,40 @@
         <v>1</v>
       </c>
       <c r="T10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11" s="2">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2">
         <v>8</v>
       </c>
-      <c r="B11" s="2">
-        <v>0</v>
-      </c>
       <c r="C11" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D11" s="2">
-        <f t="shared" ref="D11" si="2">T11</f>
+        <f t="shared" ref="D11" si="4">T11</f>
         <v>255</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="G11" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="2"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
       </c>
       <c r="I11" s="3">
-        <v>46086</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>46087.424930092595</v>
       </c>
       <c r="J11" s="2">
         <v>0</v>
@@ -1083,7 +1141,7 @@
         <v>1</v>
       </c>
       <c r="T11" s="1">
-        <f t="shared" ref="T11" si="3">SUMPRODUCT(L$2:S$2,L11:S11)</f>
+        <f t="shared" ref="T11" si="5">SUMPRODUCT(L$2:S$2,L11:S11)</f>
         <v>255</v>
       </c>
     </row>

--- a/.schema/MHR_SHOKUI_NINKA.xlsx
+++ b/.schema/MHR_SHOKUI_NINKA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KTC0966\git\sample\.schema\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t_fuk\git\sample\.schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4148D4D3-A50E-485B-ADEF-91585C52FE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B41E075-58BB-44B1-9B6E-B2360A1EC2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EMARF.MHR_SHOKUI_NINKA" sheetId="1" r:id="rId1"/>
@@ -586,14 +586,14 @@
       <c r="F3" s="6"/>
       <c r="G3" s="7">
         <f t="shared" ref="G3:G12" ca="1" si="0">NOW()</f>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="H3" s="4">
         <v>0</v>
       </c>
       <c r="I3" s="7">
         <f t="shared" ref="I3:I12" ca="1" si="1">NOW()</f>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="J3" s="4">
         <v>0</v>
@@ -619,21 +619,21 @@
         <v>10</v>
       </c>
       <c r="D4" s="4">
-        <f>T4</f>
+        <f t="shared" ref="D4:D12" si="2">T4</f>
         <v>0</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="H4" s="4">
         <v>0</v>
       </c>
       <c r="I4" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="J4" s="4">
         <v>0</v>
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="T4" s="1">
-        <f t="shared" ref="T4:T12" si="2">SUMPRODUCT(L$2:S$2,L4:S4)</f>
+        <f t="shared" ref="T4:T12" si="3">SUMPRODUCT(L$2:S$2,L4:S4)</f>
         <v>0</v>
       </c>
     </row>
@@ -678,21 +678,21 @@
         <v>10</v>
       </c>
       <c r="D5" s="4">
-        <f>T5</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="H5" s="4">
         <v>0</v>
       </c>
       <c r="I5" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="J5" s="4">
         <v>0</v>
@@ -722,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="T5" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="U5" s="1" t="s">
@@ -740,21 +740,21 @@
         <v>10</v>
       </c>
       <c r="D6" s="4">
-        <f>T6</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="H6" s="4">
         <v>0</v>
       </c>
       <c r="I6" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="J6" s="4">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="T6" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="U6" s="1" t="s">
@@ -802,21 +802,21 @@
         <v>10</v>
       </c>
       <c r="D7" s="4">
-        <f>T7</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="H7" s="4">
         <v>0</v>
       </c>
       <c r="I7" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="J7" s="4">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>1</v>
       </c>
       <c r="T7" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="U7" s="1" t="s">
@@ -864,21 +864,21 @@
         <v>10</v>
       </c>
       <c r="D8" s="4">
-        <f>T8</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="H8" s="4">
         <v>0</v>
       </c>
       <c r="I8" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="J8" s="4">
         <v>0</v>
@@ -908,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="T8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="U8" s="1" t="s">
@@ -926,21 +926,21 @@
         <v>10</v>
       </c>
       <c r="D9" s="4">
-        <f>T9</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
       </c>
       <c r="I9" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="J9" s="4">
         <v>0</v>
@@ -970,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="T9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="U9" s="1" t="s">
@@ -988,21 +988,21 @@
         <v>10</v>
       </c>
       <c r="D10" s="4">
-        <f>T10</f>
+        <f t="shared" si="2"/>
         <v>63</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
       <c r="G10" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="H10" s="4">
         <v>0</v>
       </c>
       <c r="I10" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="J10" s="4">
         <v>0</v>
@@ -1032,7 +1032,7 @@
         <v>1</v>
       </c>
       <c r="T10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>63</v>
       </c>
       <c r="U10" s="1" t="s">
@@ -1050,21 +1050,21 @@
         <v>10</v>
       </c>
       <c r="D11" s="4">
-        <f>T11</f>
+        <f t="shared" si="2"/>
         <v>127</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="H11" s="4">
         <v>0</v>
       </c>
       <c r="I11" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="J11" s="4">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>1</v>
       </c>
       <c r="T11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>127</v>
       </c>
       <c r="U11" s="1" t="s">
@@ -1112,21 +1112,21 @@
         <v>10</v>
       </c>
       <c r="D12" s="4">
-        <f>T12</f>
+        <f t="shared" si="2"/>
         <v>255</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="7">
         <f t="shared" ca="1" si="0"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="H12" s="4">
         <v>0</v>
       </c>
       <c r="I12" s="7">
         <f t="shared" ca="1" si="1"/>
-        <v>46225.640345949076</v>
+        <v>46250.454815740741</v>
       </c>
       <c r="J12" s="4">
         <v>0</v>
@@ -1156,7 +1156,7 @@
         <v>1</v>
       </c>
       <c r="T12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>255</v>
       </c>
       <c r="U12" s="1" t="s">
